--- a/financial/Poseidon_Financial_Model.xlsx
+++ b/financial/Poseidon_Financial_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shinjifujiwara/code/poseidon-mit.github.io/financial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E880DAE-B1ED-D44D-8209-544E92A52C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C7BF79-597C-974A-9CC5-99A8580EE0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="1" r:id="rId1"/>
@@ -15409,7 +15409,7 @@
         <v>0.35902878315706821</v>
       </c>
       <c r="AL23" s="79">
-        <f t="shared" si="6"/>
+        <f>AL8/AL9</f>
         <v>0.35803629527872172</v>
       </c>
     </row>
